--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1349" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1442" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>
@@ -55,6 +55,24 @@
   </si>
   <si>
     <t>n_obs</t>
+  </si>
+  <si>
+    <t>ANTIQUE</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>loaf bread</t>
+  </si>
+  <si>
+    <t>medium nga putos</t>
+  </si>
+  <si>
+    <t>tama-tama nga putos</t>
+  </si>
+  <si>
+    <t>medium packs</t>
   </si>
 </sst>
 </file>
@@ -100,7 +118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -128,47 +146,93 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1">
         <v>7</v>
       </c>
     </row>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1442" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1499" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>
@@ -118,7 +118,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -146,93 +146,47 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1">
         <v>7</v>
       </c>
     </row>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1499" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1594" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1594" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1632" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1632" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1651" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1651" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1727" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1727" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1822" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1822" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1860" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1860" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1898" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1898" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1936" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1936" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1974" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1974" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1993" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1993" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2012" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2012" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2050" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2050" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2069" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2069" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2088" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2088" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2107" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2107" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2164" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2164" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2221" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2221" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2259" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
+++ b/outputs/build/diagnostics/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2259" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2335" uniqueCount="20">
   <si>
     <t>pull_province</t>
   </si>
